--- a/BOM_驱动板.xlsx
+++ b/BOM_驱动板.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board1_PCB1_2026-07-14" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_双路有刷电机驱动板_DRV8701E_PCB_2026" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="105">
   <si>
     <t>No.</t>
   </si>
@@ -46,316 +46,277 @@
     <t>1</t>
   </si>
   <si>
-    <t>220uF/35V</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>CAP-TH_BD8.0-P3.50-D0.5-FD</t>
-  </si>
-  <si>
-    <t>220uF35V8x12KM</t>
-  </si>
-  <si>
-    <t>Econd(米朗电子)</t>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C1,C6</t>
+  </si>
+  <si>
+    <t>C0805</t>
+  </si>
+  <si>
+    <t>CGA0805X5R106K350MT</t>
+  </si>
+  <si>
+    <t>HRE(芯声)</t>
+  </si>
+  <si>
+    <t>C6119888</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C2,C4,C7,C9</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>YAGEO(国巨)</t>
+  </si>
+  <si>
+    <t>C14663</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C3,C5,C8,C10,C12,C13,C14</t>
+  </si>
+  <si>
+    <t>CL10A105KB8NNNC</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>C15849</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD8.0-P3.50-D0.6-FD</t>
+  </si>
+  <si>
+    <t>ERS1VM221F12OT</t>
+  </si>
+  <si>
+    <t>AISHI(艾华集团)</t>
+  </si>
+  <si>
+    <t>C106697</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1N5819HW-7-F</t>
+  </si>
+  <si>
+    <t>D1,D2</t>
+  </si>
+  <si>
+    <t>SOD-123_L2.7-W1.6-LS3.7-RD</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>LCSC</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C2,C8,C9</t>
-  </si>
-  <si>
-    <t>C0805</t>
-  </si>
-  <si>
-    <t>CL21B105KBFNNNE</t>
-  </si>
-  <si>
-    <t>SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>C28323</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C3,C10</t>
-  </si>
-  <si>
-    <t>GRM21BR61H106KE43L</t>
-  </si>
-  <si>
-    <t>muRata(村田)</t>
-  </si>
-  <si>
-    <t>C440198</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C4,C6,C11,C13</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB104</t>
-  </si>
-  <si>
-    <t>YAGEO(国巨)</t>
-  </si>
-  <si>
-    <t>C14663</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>C5,C7,C12,C14</t>
-  </si>
-  <si>
-    <t>CL10A105KB8NNNC</t>
-  </si>
-  <si>
-    <t>C15849</t>
+    <t>DIODES(美台)</t>
+  </si>
+  <si>
+    <t>C82544</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>1N5819HW</t>
-  </si>
-  <si>
-    <t>D1,D2</t>
-  </si>
-  <si>
-    <t>SOD-123_L2.7-W1.6-LS3.8-RD</t>
-  </si>
-  <si>
-    <t>GOODWORK(固得沃克)</t>
-  </si>
-  <si>
-    <t>C41431974</t>
+    <t>NCD0805R1</t>
+  </si>
+  <si>
+    <t>LED1,LED2</t>
+  </si>
+  <si>
+    <t>LED0805-R-RD</t>
+  </si>
+  <si>
+    <t>国星光电</t>
+  </si>
+  <si>
+    <t>C84256</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>0Ω</t>
-  </si>
-  <si>
-    <t>J1</t>
+    <t>KF301-5.0-2P</t>
+  </si>
+  <si>
+    <t>P1,P2,P3</t>
+  </si>
+  <si>
+    <t>CONN-TH_P5.00_KF301-5.0-2P</t>
+  </si>
+  <si>
+    <t>KEFA(科发)</t>
+  </si>
+  <si>
+    <t>C474881</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>PH2.54-01-03PZS</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-M-R2-C3-S2.54</t>
+  </si>
+  <si>
+    <t>XUNPU(讯普)</t>
+  </si>
+  <si>
+    <t>C7501594</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>TPH1R403NL</t>
+  </si>
+  <si>
+    <t>Q1,Q2,Q3,Q4,Q5,Q6,Q7,Q8</t>
+  </si>
+  <si>
+    <t>DSOP-8_L5.0-W5.0-P1.27-LS6.0-BL-EP</t>
+  </si>
+  <si>
+    <t>TOSHIBA(东芝)</t>
+  </si>
+  <si>
+    <t>C83440</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>R1,R2,R3,R4</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>FRC0603J103 TS</t>
+  </si>
+  <si>
+    <t>FOJAN(富捷)</t>
+  </si>
+  <si>
+    <t>C2930027</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2.2kΩ</t>
+  </si>
+  <si>
+    <t>R5,R6</t>
   </si>
   <si>
     <t>R0805</t>
   </si>
   <si>
-    <t>0805W8F0000T5E</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C17477</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>KT-0805G</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>LED0805-R-RD</t>
-  </si>
-  <si>
-    <t>KENTO</t>
-  </si>
-  <si>
-    <t>C2297</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>KT-0805Y</t>
-  </si>
-  <si>
-    <t>LED2</t>
-  </si>
-  <si>
-    <t>C2296</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>KF301-2P接线端子</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>CONN-TH_XY301V-A-5.0-2P</t>
-  </si>
-  <si>
-    <t>C9900016950</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>电机1接口</t>
-  </si>
-  <si>
-    <t>P2</t>
+    <t>RC0805FR-072K2L</t>
+  </si>
+  <si>
+    <t>C114561</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>电机2接口</t>
-  </si>
-  <si>
-    <t>P3</t>
+    <t>SS12D10G4 071</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>SW-TH_SHOU-HAN_SS12D10G4</t>
+  </si>
+  <si>
+    <t>SHOU HAN(首韩)</t>
+  </si>
+  <si>
+    <t>C2887259</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>SH-GH1.25-6PWB</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>SW-SMD_SH-GH1.25-6PWB</t>
-  </si>
-  <si>
-    <t>SHOU HAN(首韩)</t>
-  </si>
-  <si>
-    <t>C42372473</t>
+    <t>DRV8701ERGER</t>
+  </si>
+  <si>
+    <t>U1,U2</t>
+  </si>
+  <si>
+    <t>VQFN-24_L4.0-W4.0-P0.50-BL-EP2.5</t>
+  </si>
+  <si>
+    <t>TI(德州仪器)</t>
+  </si>
+  <si>
+    <t>C90964</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>TPH1R403NL</t>
-  </si>
-  <si>
-    <t>Q1,Q2,Q3,Q4,Q5,Q6,Q7,Q8</t>
-  </si>
-  <si>
-    <t>DSOP-8_L5.0-W5.0-P1.27-LS6.0-BL-EP</t>
-  </si>
-  <si>
-    <t>TOSHIBA(东芝)</t>
-  </si>
-  <si>
-    <t>C83440</t>
+    <t>SN74HC125PWR</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>TSSOP-14_L5.0-W4.4-P0.65-LS6.5-BL</t>
+  </si>
+  <si>
+    <t>C132994</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>R1,R2,R3,R4</t>
-  </si>
-  <si>
-    <t>0805W8F2201T5E</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>2.2K</t>
-  </si>
-  <si>
-    <t>R5,R6</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>SK-12F04-G050</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>SW-TH_G-SWITCH_SK-12F04-G050</t>
-  </si>
-  <si>
-    <t>G-Switch(品赞)</t>
-  </si>
-  <si>
-    <t>C2848876</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>SN74HC125PWR</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>TSSOP-14_L5.0-W4.4-P0.65-LS6.5-BL</t>
-  </si>
-  <si>
-    <t>TI(德州仪器)</t>
-  </si>
-  <si>
-    <t>C132994</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>DRV8701ERGER</t>
-  </si>
-  <si>
-    <t>U2,U4</t>
-  </si>
-  <si>
-    <t>VQFN-24_L4.0-W4.0-P0.50-BL-EP2.5</t>
-  </si>
-  <si>
-    <t>C90964</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>LR8341A-T33</t>
   </si>
   <si>
-    <t>U3</t>
+    <t>U4</t>
   </si>
   <si>
     <t>SOT-23-3L_L2.9-W1.6-P1.90-LS2.8-BL</t>
@@ -741,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -784,7 +745,7 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -816,7 +777,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -848,7 +809,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -880,7 +841,7 @@
         <v>31</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
@@ -912,28 +873,28 @@
         <v>38</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -941,31 +902,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -973,31 +934,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
         <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -1005,31 +966,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
         <v>58</v>
       </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>56</v>
-      </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -1037,31 +998,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -1069,31 +1030,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -1101,31 +1062,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -1133,31 +1094,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -1165,31 +1126,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1197,31 +1158,31 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
@@ -1229,199 +1190,39 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H18" t="s">
-        <v>99</v>
-      </c>
-      <c r="I18" t="s">
-        <v>100</v>
-      </c>
-      <c r="J18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" t="s">
-        <v>102</v>
-      </c>
-      <c r="H19" t="s">
-        <v>105</v>
-      </c>
-      <c r="I19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H20" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" t="s">
-        <v>111</v>
-      </c>
-      <c r="J20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" t="s">
-        <v>113</v>
-      </c>
-      <c r="H21" t="s">
-        <v>116</v>
-      </c>
-      <c r="I21" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
